--- a/data/Август_2026.xlsx
+++ b/data/Август_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE3E210-F78E-427B-BC96-08A53C0E8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCCA458-A481-4C7A-AEA1-7045DB1B1DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="283">
   <si>
     <t>№ п/п</t>
   </si>
@@ -857,6 +857,33 @@
   </si>
   <si>
     <t>Не соответствует марка стали и /или материал</t>
+  </si>
+  <si>
+    <t>Не проведён технический контроль продукции, сырья, материалов, комплектующих</t>
+  </si>
+  <si>
+    <t>Усилить контроль за исполнителем. Отв Бригадир</t>
+  </si>
+  <si>
+    <t>1. Направить информацию о выявленном несоответствии поставщику. 
+Отв. отдел закупок
+2. Усилить контроль отв. сменный мастер/бригадир</t>
+  </si>
+  <si>
+    <t>Скрытый дефект в продукции поставщиков</t>
+  </si>
+  <si>
+    <t>Усилить контроль, провести беседу с исполнителем</t>
+  </si>
+  <si>
+    <t>Низкая оборачиваемость товаров на складе</t>
+  </si>
+  <si>
+    <t>Минимизировать количество перестановок для такого рода конструкций. Отв. Отдел логистики</t>
+  </si>
+  <si>
+    <t>Произвести ремонт авт. линии сварки опор.
+Отв. технический департамент.</t>
   </si>
 </sst>
 </file>
@@ -924,7 +951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -964,9 +991,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1280,13 +1304,13 @@
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.85546875" style="1" customWidth="1"/>
     <col min="10" max="10" width="33.140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" style="1" customWidth="1"/>
@@ -1612,11 +1636,21 @@
       <c r="L6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1791,7 +1825,7 @@
       <c r="M10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="5" t="s">
         <v>70</v>
       </c>
       <c r="O10" s="5" t="s">
@@ -2754,11 +2788,21 @@
       <c r="L28" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
+      <c r="M28" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="P28" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="R28" s="5"/>
     </row>
     <row r="29" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -2798,11 +2842,21 @@
       <c r="L29" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
+      <c r="M29" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="R29" s="5"/>
     </row>
     <row r="30" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -3636,11 +3690,21 @@
       <c r="L46" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
+      <c r="M46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>276</v>
+      </c>
       <c r="R46" s="5"/>
     </row>
     <row r="47" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -3790,11 +3854,21 @@
       <c r="L49" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
+      <c r="M49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="R49" s="5"/>
     </row>
     <row r="50" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -4466,11 +4540,21 @@
       <c r="L62" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="M62" s="4"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
+      <c r="M62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="P62" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q62" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="R62" s="5"/>
     </row>
     <row r="63" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">

--- a/data/Август_2026.xlsx
+++ b/data/Август_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCCA458-A481-4C7A-AEA1-7045DB1B1DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5916FEB6-FD0A-44FE-BEE7-2D106757D627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="285">
   <si>
     <t>№ п/п</t>
   </si>
@@ -884,6 +884,15 @@
   <si>
     <t>Произвести ремонт авт. линии сварки опор.
 Отв. технический департамент.</t>
+  </si>
+  <si>
+    <t>1. Направить информацию поставщику о выявленном несоответствии (сварной шов) Отв. отдел закупок
+2. Усилить контроль за данным видом изделий перед взятием в работу. Отв. сменный мастер/ бригадир</t>
+  </si>
+  <si>
+    <t>1. Проводить контроль первой детали
+2. Провести беседу с исполнителем о корректности чтения КД и о проведении контроля
+Отв. сменный мастер/бригадир</t>
   </si>
 </sst>
 </file>
@@ -1690,11 +1699,21 @@
       <c r="L7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="M7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1778,11 +1797,21 @@
       <c r="L9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
+      <c r="M9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>284</v>
+      </c>
       <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
